--- a/data/trans_orig/P21D_4_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262773</t>
+          <t>262513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296259</t>
+          <t>296213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561242</t>
+          <t>561165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>438467</t>
+          <t>439407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445207</t>
+          <t>445490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1097256</t>
+          <t>1097100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1104132</t>
+          <t>1103939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>324254</t>
+          <t>326652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323971</t>
+          <t>324548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328660</t>
+          <t>328657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652253</t>
+          <t>652300</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658912</t>
+          <t>658915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>402033</t>
+          <t>401877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502749</t>
+          <t>502884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514040</t>
+          <t>513807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>909122</t>
+          <t>908951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>920865</t>
+          <t>920486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1655083</t>
+          <t>1654336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1663102</t>
+          <t>1662982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1571251</t>
+          <t>1570831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1583779</t>
+          <t>1584206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3230996</t>
+          <t>3229365</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3245895</t>
+          <t>3245642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_4_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>265906</t>
+          <t>287463</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262513</t>
+          <t>283756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>298551</t>
+          <t>322861</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296213</t>
+          <t>320030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>564456</t>
+          <t>610324</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561165</t>
+          <t>607170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>323509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565727</t>
+          <t>611632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442967</t>
+          <t>498345</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439407</t>
+          <t>493688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445490</t>
+          <t>500929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1101357</t>
+          <t>968553</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1097100</t>
+          <t>963746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1103939</t>
+          <t>971089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446772</t>
+          <t>502802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1105162</t>
+          <t>973010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>329834</t>
+          <t>375589</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326652</t>
+          <t>370998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>327319</t>
+          <t>376212</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324548</t>
+          <t>373025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328657</t>
+          <t>377547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>657151</t>
+          <t>751800</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652300</t>
+          <t>747297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658915</t>
+          <t>753905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>328824</t>
+          <t>378053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>659661</t>
+          <t>754636</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>659661</t>
+          <t>754636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>659661</t>
+          <t>754636</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>406269</t>
+          <t>431628</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401877</t>
+          <t>427495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>510131</t>
+          <t>482675</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502884</t>
+          <t>475132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513807</t>
+          <t>486340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>916399</t>
+          <t>914304</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>908951</t>
+          <t>906326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>920486</t>
+          <t>918502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517309</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>925261</t>
+          <t>923370</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,67 +2132,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>26447</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1660397</t>
+          <t>1564889</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1654336</t>
+          <t>1559690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1662982</t>
+          <t>1567125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,67 +2245,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1578968</t>
+          <t>1680092</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1570831</t>
+          <t>1672380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1584206</t>
+          <t>1685552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3807</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>3244981</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3236041</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3250909</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3807</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3239365</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3229365</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3245642</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
